--- a/excel_config/indir/世界地图.xlsx
+++ b/excel_config/indir/世界地图.xlsx
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>int[]</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>[146,181]</t>
+          <t>146:181</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>["坊市","委托","补给"]</t>
+          <t>坊市:委托:补给</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>[350,106]</t>
+          <t>350:106</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>["坊市","传送阵","宗门驻地"]</t>
+          <t>坊市:传送阵:宗门驻地</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>[565,196]</t>
+          <t>565:196</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>["摆渡","补给","情报"]</t>
+          <t>摆渡:补给:情报</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>[650,371]</t>
+          <t>650:371</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>["坊市","客栈","委托"]</t>
+          <t>坊市:客栈:委托</t>
         </is>
       </c>
     </row>
@@ -1652,17 +1652,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>int[]</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>["山谷","狼群","迷雾"]</t>
+          <t>山谷:狼群:迷雾</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>["妖丹","狼皮","灵草"]</t>
+          <t>妖丹:狼皮:灵草</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>[160,430]</t>
+          <t>160:430</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>["剧情","狼患调查"]</t>
+          <t>剧情:狼患调查</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>["灵泉","竹林","药圃"]</t>
+          <t>灵泉:竹林:药圃</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>["灵草","泉水精华"]</t>
+          <t>灵草:泉水精华</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>[75,406]</t>
+          <t>75:406</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>["采集","恢复"]</t>
+          <t>采集:恢复</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>["剑意","遗迹","禁制"]</t>
+          <t>剑意:遗迹:禁制</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>["断剑","剑诀残页"]</t>
+          <t>断剑:剑诀残页</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>[270,371]</t>
+          <t>270:371</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>["秘境入口","剑冢试炼"]</t>
+          <t>秘境入口:剑冢试炼</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>["药圃","雾溪","灵草"]</t>
+          <t>药圃:雾溪:灵草</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>["雾隐草","灵果"]</t>
+          <t>雾隐草:灵果</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>[430,292]</t>
+          <t>430:292</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>["采集","炼丹材料"]</t>
+          <t>采集:炼丹材料</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>["残阵","阵灵","禁制"]</t>
+          <t>残阵:阵灵:禁制</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>["阵核碎片","筑基功法"]</t>
+          <t>阵核碎片:筑基功法</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>[530,312]</t>
+          <t>530:312</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>["残阵调查","精英遭遇"]</t>
+          <t>残阵调查:精英遭遇</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>int[][]</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -2241,27 +2241,27 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>["山林","灵泉","妖兽巢穴"]</t>
+          <t>山林:灵泉:妖兽巢穴</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>["灵草","妖丹","寒潭珠"]</t>
+          <t>灵草:妖丹:寒潭珠</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>[[30,350],[280,350],[280,500],[30,500]]</t>
+          <t>30:350|280:350|280:500|30:500</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>["qingshi_market"]</t>
+          <t>qingshi_market</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>["wild_wolf_valley","spirit_spring_valley","ancient_sword_tomb"]</t>
+          <t>wild_wolf_valley:spirit_spring_valley:ancient_sword_tomb</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -2297,29 +2297,25 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>["沼泽","毒雾","妖兽"]</t>
+          <t>沼泽:毒雾:妖兽</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>["毒囊","沼泽灵草"]</t>
+          <t>毒囊:沼泽灵草</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>[[500,20],[750,20],[750,170],[500,170]]</t>
+          <t>500:20|750:20|750:170|500:170</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>["yunlan_city","tianhe_ferry"]</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>yunlan_city:tianhe_ferry</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>blackwater_marsh</t>
@@ -2353,27 +2349,27 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>["溪谷","雾瘴","残阵"]</t>
+          <t>溪谷:雾瘴:残阵</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>["雾隐草","阵核碎片","筑基丹药材料"]</t>
+          <t>雾隐草:阵核碎片:筑基丹药材料</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>[[390,245],[560,245],[560,345],[390,345]]</t>
+          <t>390:245|560:245|560:345|390:345</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>["yunlan_city","tianhe_ferry"]</t>
+          <t>yunlan_city:tianhe_ferry</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>["mist_creek_herb_garden","sealed_creek_ruins"]</t>
+          <t>mist_creek_herb_garden:sealed_creek_ruins</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
